--- a/data/trans_dic/P22$mutaSS-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,31</t>
+          <t>1,93; 5,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,53</t>
+          <t>1,08; 4,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,39</t>
+          <t>0,25; 2,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,42</t>
+          <t>1,05; 7,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,05</t>
+          <t>3,61; 7,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,3</t>
+          <t>1,33; 4,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,18</t>
+          <t>0,52; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,84</t>
+          <t>3,27; 5,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,65</t>
+          <t>1,53; 3,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,14</t>
+          <t>0,62; 2,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,97</t>
+          <t>0,69; 3,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,3</t>
+          <t>1,64; 4,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,58</t>
+          <t>1,79; 4,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,06</t>
+          <t>0,99; 3,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,0</t>
+          <t>0,6; 5,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,36</t>
+          <t>2,13; 5,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,18</t>
+          <t>0,94; 3,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,15</t>
+          <t>0,19; 2,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,74</t>
+          <t>0,17; 1,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,04</t>
+          <t>2,19; 4,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,41</t>
+          <t>1,64; 3,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,24</t>
+          <t>0,83; 2,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,59</t>
+          <t>0,55; 2,71</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,03</t>
+          <t>2,76; 6,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,1</t>
+          <t>1,52; 4,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,57</t>
+          <t>1,71; 4,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,37</t>
+          <t>1,92; 5,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,07</t>
+          <t>2,27; 5,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,04</t>
+          <t>0,83; 3,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,18</t>
+          <t>1,02; 3,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,29</t>
+          <t>1,17; 3,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,97</t>
+          <t>2,84; 5,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,24</t>
+          <t>1,35; 3,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,28</t>
+          <t>1,64; 3,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,87</t>
+          <t>1,81; 3,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,94</t>
+          <t>3,67; 7,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,4</t>
+          <t>2,18; 5,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,12</t>
+          <t>1,44; 4,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,21</t>
+          <t>1,05; 4,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,33</t>
+          <t>1,47; 4,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,08</t>
+          <t>1,84; 4,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,2</t>
+          <t>0,48; 2,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,88</t>
+          <t>0,63; 1,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,46</t>
+          <t>2,89; 5,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,72</t>
+          <t>2,36; 4,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,74</t>
+          <t>1,2; 2,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,77</t>
+          <t>1,1; 2,87</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,56</t>
+          <t>2,11; 5,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,59</t>
+          <t>1,42; 4,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,29</t>
+          <t>1,85; 5,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,37</t>
+          <t>1,03; 3,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,63</t>
+          <t>2,51; 6,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,62</t>
+          <t>0,72; 3,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,51</t>
+          <t>0,72; 3,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,26</t>
+          <t>2,11; 4,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,46</t>
+          <t>2,66; 5,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,47</t>
+          <t>1,3; 3,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,76</t>
+          <t>1,54; 3,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,39</t>
+          <t>1,77; 3,37</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,36</t>
+          <t>1,47; 5,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,95</t>
+          <t>0,67; 4,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,02</t>
+          <t>0,78; 4,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,96</t>
+          <t>1,89; 4,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,17</t>
+          <t>0,82; 3,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,86</t>
+          <t>0,8; 4,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,1</t>
+          <t>0,55; 2,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,83</t>
+          <t>0,99; 4,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,89</t>
+          <t>1,42; 3,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,36</t>
+          <t>0,93; 3,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,81</t>
+          <t>0,88; 2,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,09</t>
+          <t>1,38; 4,15</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,98</t>
+          <t>0,39; 4,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,33</t>
+          <t>0,62; 3,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,74</t>
+          <t>1,45; 4,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,31</t>
+          <t>0,34; 3,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,1</t>
+          <t>0,29; 3,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,61</t>
+          <t>0,79; 2,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,09</t>
+          <t>0,6; 3,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,2</t>
+          <t>0,5; 2,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,16</t>
+          <t>0,39; 2,32</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,96</t>
+          <t>1,32; 2,97</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,3</t>
+          <t>2,98; 4,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,28</t>
+          <t>2,13; 3,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,85</t>
+          <t>1,75; 2,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,36</t>
+          <t>1,96; 3,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,04</t>
+          <t>2,75; 4,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,63</t>
+          <t>1,59; 2,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,75</t>
+          <t>0,97; 1,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,11</t>
+          <t>1,31; 2,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,99</t>
+          <t>3,03; 3,96</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,79</t>
+          <t>2,0; 2,77</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,14</t>
+          <t>1,47; 2,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,54</t>
+          <t>1,78; 2,53</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9156; 26170</t>
+          <t>9534; 26653</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5782; 20520</t>
+          <t>4893; 19348</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1041; 9979</t>
+          <t>1060; 10162</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4080; 25691</t>
+          <t>4219; 29202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17701; 37622</t>
+          <t>16865; 36142</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5785; 18486</t>
+          <t>5703; 18579</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2633; 12597</t>
+          <t>2055; 11910</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5343</t>
+          <t>0; 6221</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30234; 56057</t>
+          <t>31436; 55290</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13585; 32257</t>
+          <t>13490; 32302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5050; 17420</t>
+          <t>5011; 17881</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4364; 28343</t>
+          <t>4903; 27497</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12177; 31503</t>
+          <t>12021; 30763</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12990; 31492</t>
+          <t>12298; 32144</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5787; 18065</t>
+          <t>5819; 19754</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2472; 21197</t>
+          <t>2534; 24013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14328; 33531</t>
+          <t>13299; 33247</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5078; 19416</t>
+          <t>5750; 19941</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1617; 12076</t>
+          <t>1070; 12254</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>968; 8919</t>
+          <t>854; 8792</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29493; 54823</t>
+          <t>29780; 56532</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20944; 44199</t>
+          <t>21239; 44921</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9520; 25783</t>
+          <t>9513; 26538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4929; 24217</t>
+          <t>5179; 25318</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17734; 38519</t>
+          <t>17658; 39309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9725; 27964</t>
+          <t>10344; 29448</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11098; 30516</t>
+          <t>11440; 28664</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10505; 28789</t>
+          <t>10301; 28476</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15332; 34953</t>
+          <t>15637; 34942</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6242; 21615</t>
+          <t>5935; 22003</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6676; 21058</t>
+          <t>6732; 21628</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6802; 17857</t>
+          <t>6327; 16920</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36619; 66035</t>
+          <t>37744; 67250</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19732; 45087</t>
+          <t>18869; 43448</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21446; 43565</t>
+          <t>21836; 44595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19544; 41703</t>
+          <t>19537; 40945</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19057; 41110</t>
+          <t>19018; 41261</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12730; 33201</t>
+          <t>13406; 33959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10002; 26644</t>
+          <t>9322; 27334</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9144; 37417</t>
+          <t>9297; 38323</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7208; 22267</t>
+          <t>7582; 22158</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12226; 31298</t>
+          <t>11310; 30189</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3074; 14232</t>
+          <t>3106; 14570</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4373; 13372</t>
+          <t>4525; 13505</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30119; 56329</t>
+          <t>29793; 55802</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29661; 58109</t>
+          <t>29067; 57704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14765; 35470</t>
+          <t>15468; 36640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18712; 44400</t>
+          <t>17663; 46007</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7945; 21504</t>
+          <t>8149; 22933</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6091; 19731</t>
+          <t>6084; 19300</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8975; 25152</t>
+          <t>8787; 25345</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6134; 18940</t>
+          <t>5803; 18338</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10620; 26708</t>
+          <t>10118; 26220</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3135; 16195</t>
+          <t>3207; 17223</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3562; 17435</t>
+          <t>3576; 17300</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11220; 23220</t>
+          <t>11521; 23366</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21367; 43154</t>
+          <t>20995; 43111</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11380; 30473</t>
+          <t>11387; 30581</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15560; 36563</t>
+          <t>14954; 37323</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19820; 37476</t>
+          <t>19587; 37337</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4591; 15681</t>
+          <t>4294; 16123</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2041; 12252</t>
+          <t>2060; 14195</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2557; 13434</t>
+          <t>2604; 13603</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7101; 18270</t>
+          <t>6954; 18332</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2832; 14292</t>
+          <t>2826; 12646</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2828; 13660</t>
+          <t>2844; 14731</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2087; 11656</t>
+          <t>2065; 10750</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5138; 29361</t>
+          <t>6010; 28218</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9420; 24700</t>
+          <t>9026; 24121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6835; 22326</t>
+          <t>6180; 21618</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6125; 19956</t>
+          <t>6260; 20867</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12973; 39940</t>
+          <t>13479; 40531</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>821; 10368</t>
+          <t>809; 9974</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 7517</t>
+          <t>0; 6488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1632; 8571</t>
+          <t>1596; 9079</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4491; 13413</t>
+          <t>4093; 13346</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1125; 11054</t>
+          <t>1126; 11153</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2109; 12043</t>
+          <t>1119; 11888</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 11104</t>
+          <t>0; 10943</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3572; 11106</t>
+          <t>3348; 10311</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3650; 16731</t>
+          <t>3264; 16531</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3219; 14082</t>
+          <t>3166; 14693</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2529; 14196</t>
+          <t>2534; 15222</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9638; 21003</t>
+          <t>9383; 21042</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>97240; 140671</t>
+          <t>97585; 139614</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>73191; 112473</t>
+          <t>72908; 111940</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60680; 96571</t>
+          <t>59381; 95608</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>70274; 116316</t>
+          <t>67672; 116004</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>94062; 136296</t>
+          <t>92763; 135492</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>56292; 93592</t>
+          <t>56535; 91782</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33448; 61918</t>
+          <t>34357; 63040</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>48184; 77324</t>
+          <t>47796; 77505</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>200172; 265303</t>
+          <t>201647; 263294</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>139526; 194698</t>
+          <t>139820; 193417</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>103529; 148426</t>
+          <t>101890; 146255</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>126393; 180810</t>
+          <t>126820; 180417</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutaSS-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,4</t>
+          <t>1,82; 5,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,27</t>
+          <t>1,25; 4,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,43</t>
+          <t>0,25; 2,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,3</t>
+          <t>0,74; 6,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,73</t>
+          <t>3,76; 7,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,32</t>
+          <t>1,36; 4,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,01</t>
+          <t>0,59; 2,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,76</t>
+          <t>3,21; 6,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,66</t>
+          <t>1,59; 3,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,2</t>
+          <t>0,6; 2,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,86</t>
+          <t>0,59; 3,57</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,2</t>
+          <t>1,64; 4,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,68</t>
+          <t>1,87; 4,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,35</t>
+          <t>1,06; 3,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,67</t>
+          <t>0,52; 4,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,32</t>
+          <t>2,11; 5,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,27</t>
+          <t>0,85; 3,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,18</t>
+          <t>0,19; 2,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,72</t>
+          <t>0,35; 2,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,16</t>
+          <t>2,2; 4,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,46</t>
+          <t>1,68; 3,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,3</t>
+          <t>0,77; 2,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,71</t>
+          <t>0,6; 2,74</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,15</t>
+          <t>2,65; 5,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,32</t>
+          <t>1,51; 4,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,29</t>
+          <t>1,57; 4,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,31</t>
+          <t>1,74; 4,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,07</t>
+          <t>2,07; 4,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,1</t>
+          <t>0,94; 3,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,27</t>
+          <t>1,01; 3,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,12</t>
+          <t>1,14; 2,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,06</t>
+          <t>2,88; 5,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,12</t>
+          <t>1,34; 3,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,35</t>
+          <t>1,54; 3,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,8</t>
+          <t>1,64; 3,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,97</t>
+          <t>3,81; 7,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,53</t>
+          <t>2,22; 6,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,23</t>
+          <t>1,47; 4,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,32</t>
+          <t>2,07; 4,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,31</t>
+          <t>1,4; 4,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,9</t>
+          <t>1,88; 5,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,25</t>
+          <t>0,48; 2,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,89</t>
+          <t>0,65; 1,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,4</t>
+          <t>2,95; 5,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,69</t>
+          <t>2,38; 4,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,83</t>
+          <t>1,18; 2,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,87</t>
+          <t>1,52; 3,09</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,93</t>
+          <t>1,9; 5,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,49</t>
+          <t>1,4; 4,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,33</t>
+          <t>1,87; 5,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,27</t>
+          <t>0,98; 3,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,5</t>
+          <t>2,7; 6,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,48</t>
+          <t>0,78; 3,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,28</t>
+          <t>2,03; 4,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,46</t>
+          <t>2,63; 5,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,49</t>
+          <t>1,29; 3,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,84</t>
+          <t>1,62; 3,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,37</t>
+          <t>1,79; 3,28</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,51</t>
+          <t>1,51; 5,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,58</t>
+          <t>0,97; 4,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,07</t>
+          <t>0,77; 4,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,98</t>
+          <t>1,67; 4,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,69</t>
+          <t>0,83; 3,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,16</t>
+          <t>0,8; 4,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,86</t>
+          <t>0,55; 3,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,64</t>
+          <t>2,19; 4,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,8</t>
+          <t>1,46; 3,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,26</t>
+          <t>1,06; 3,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,94</t>
+          <t>0,86; 2,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,15</t>
+          <t>2,21; 4,08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,79</t>
+          <t>0,39; 5,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,53</t>
+          <t>0,62; 3,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,72</t>
+          <t>1,43; 4,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,34</t>
+          <t>0,34; 3,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,06</t>
+          <t>0,29; 2,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,42</t>
+          <t>0,77; 2,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,05</t>
+          <t>0,63; 3,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,3</t>
+          <t>0,5; 2,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,32</t>
+          <t>0,38; 2,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,97</t>
+          <t>1,27; 2,86</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,27</t>
+          <t>2,95; 4,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,27</t>
+          <t>2,07; 3,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,82</t>
+          <t>1,82; 2,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,35</t>
+          <t>2,08; 3,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,01</t>
+          <t>2,74; 3,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,58</t>
+          <t>1,61; 2,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,78</t>
+          <t>0,93; 1,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,12</t>
+          <t>1,42; 2,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,96</t>
+          <t>2,98; 3,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,77</t>
+          <t>2,02; 2,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,11</t>
+          <t>1,49; 2,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,53</t>
+          <t>1,86; 2,51</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>11601</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9534; 26653</t>
+          <t>8997; 26611</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4893; 19348</t>
+          <t>5646; 19232</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1060; 10162</t>
+          <t>1044; 9369</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4219; 29202</t>
+          <t>3013; 24529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16865; 36142</t>
+          <t>17570; 36806</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5703; 18579</t>
+          <t>5843; 18162</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2055; 11910</t>
+          <t>2322; 11778</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6221</t>
+          <t>0; 7163</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31436; 55290</t>
+          <t>30838; 57748</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13490; 32302</t>
+          <t>14005; 33008</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5011; 17881</t>
+          <t>4918; 18055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4903; 27497</t>
+          <t>4510; 27514</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>12766</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12021; 30763</t>
+          <t>12036; 30105</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12298; 32144</t>
+          <t>12873; 31537</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5819; 19754</t>
+          <t>6270; 19058</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2534; 24013</t>
+          <t>2456; 21299</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13299; 33247</t>
+          <t>13190; 33376</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5750; 19941</t>
+          <t>5166; 19317</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1070; 12254</t>
+          <t>1064; 11717</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>854; 8792</t>
+          <t>1730; 10156</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29780; 56532</t>
+          <t>29948; 56388</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21239; 44921</t>
+          <t>21739; 45170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9513; 26538</t>
+          <t>8844; 25424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5179; 25318</t>
+          <t>5845; 26720</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17460</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>30369</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17658; 39309</t>
+          <t>16922; 37801</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10344; 29448</t>
+          <t>10283; 28545</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11440; 28664</t>
+          <t>10516; 29615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10301; 28476</t>
+          <t>10826; 30503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15637; 34942</t>
+          <t>14311; 34080</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5935; 22003</t>
+          <t>6647; 21855</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6732; 21628</t>
+          <t>6701; 21098</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6327; 16920</t>
+          <t>7073; 18390</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37744; 67250</t>
+          <t>38220; 66650</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18869; 43448</t>
+          <t>18694; 45391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21836; 44595</t>
+          <t>20427; 43123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19537; 40945</t>
+          <t>20418; 43129</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23431</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>31893</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19018; 41261</t>
+          <t>19758; 41375</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13406; 33959</t>
+          <t>13632; 36873</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9322; 27334</t>
+          <t>9520; 26848</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9297; 38323</t>
+          <t>14482; 33807</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7582; 22158</t>
+          <t>7218; 22305</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11310; 30189</t>
+          <t>11590; 32172</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3106; 14570</t>
+          <t>3112; 13763</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4525; 13505</t>
+          <t>4825; 14187</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29793; 55802</t>
+          <t>30489; 55231</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29067; 57704</t>
+          <t>29247; 57171</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15468; 36640</t>
+          <t>15335; 35520</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17663; 46007</t>
+          <t>21895; 44455</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27613</t>
+          <t>29409</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8149; 22933</t>
+          <t>7352; 21684</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6084; 19300</t>
+          <t>6009; 19488</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8787; 25345</t>
+          <t>8917; 25371</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5803; 18338</t>
+          <t>5992; 18701</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10118; 26220</t>
+          <t>10873; 26440</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3207; 17223</t>
+          <t>3211; 17233</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3576; 17300</t>
+          <t>3853; 17012</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11521; 23366</t>
+          <t>12324; 24753</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20995; 43111</t>
+          <t>20773; 41886</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11387; 30581</t>
+          <t>11306; 29767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14954; 37323</t>
+          <t>15796; 37072</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19587; 37337</t>
+          <t>21735; 39979</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>13982</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>26123</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4294; 16123</t>
+          <t>4409; 15902</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2060; 14195</t>
+          <t>2995; 13525</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2604; 13603</t>
+          <t>2577; 14789</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6954; 18332</t>
+          <t>6788; 18498</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2826; 12646</t>
+          <t>2840; 13388</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2844; 14731</t>
+          <t>2840; 14190</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2065; 10750</t>
+          <t>2083; 12215</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6010; 28218</t>
+          <t>9635; 19666</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9026; 24121</t>
+          <t>9309; 24658</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6180; 21618</t>
+          <t>7056; 22007</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6260; 20867</t>
+          <t>6129; 20485</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13479; 40531</t>
+          <t>18735; 34526</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>14902</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>809; 9974</t>
+          <t>820; 10766</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6488</t>
+          <t>0; 8178</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1596; 9079</t>
+          <t>1592; 8956</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4093; 13346</t>
+          <t>4434; 13597</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1126; 11153</t>
+          <t>1124; 11255</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1119; 11888</t>
+          <t>1115; 10963</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 10943</t>
+          <t>0; 11115</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3348; 10311</t>
+          <t>3570; 11028</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3264; 16531</t>
+          <t>3406; 16693</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3166; 14693</t>
+          <t>3211; 15037</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2534; 15222</t>
+          <t>2476; 14581</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9383; 21042</t>
+          <t>9855; 22161</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91149</t>
+          <t>92585</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>62739</t>
+          <t>64478</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>153888</t>
+          <t>157063</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>97585; 139614</t>
+          <t>96485; 139565</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>72908; 111940</t>
+          <t>70853; 113194</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>59381; 95608</t>
+          <t>61598; 97527</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>67672; 116004</t>
+          <t>73559; 117256</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>92763; 135492</t>
+          <t>92490; 134696</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>56535; 91782</t>
+          <t>57404; 91307</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34357; 63040</t>
+          <t>32986; 61015</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>47796; 77505</t>
+          <t>52833; 77940</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>201647; 263294</t>
+          <t>198013; 261137</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>139820; 193417</t>
+          <t>141231; 191928</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>101890; 146255</t>
+          <t>103000; 146308</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>126820; 180417</t>
+          <t>135170; 182247</t>
         </is>
       </c>
     </row>
